--- a/docs/9-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/9-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\9-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD6C15A-FD4B-43FC-9F30-B3A826A2BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B597A08-305B-408D-866A-57ECF5A07037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="222">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -705,6 +705,9 @@
   </si>
   <si>
     <t>Review</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -814,9 +817,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -825,6 +825,9 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1358,7 +1361,7 @@
       <c r="E2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -1387,7 +1390,7 @@
       <c r="E3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1416,10 +1419,10 @@
       <c r="E4" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>94</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -1445,10 +1448,10 @@
       <c r="E5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>93</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1602,19 +1605,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1963,19 +1966,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2254,19 +2257,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2615,19 +2618,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3046,19 +3049,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3115,7 +3118,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>98</v>
@@ -3150,7 +3153,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>215</v>
@@ -3182,7 +3185,7 @@
         <v>213</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>97</v>
@@ -3217,7 +3220,7 @@
         <v>213</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>97</v>
@@ -3252,7 +3255,7 @@
         <v>46031</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>97</v>
@@ -3287,7 +3290,7 @@
         <v>46121</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>97</v>

--- a/docs/9-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/9-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\9-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B597A08-305B-408D-866A-57ECF5A07037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240A7ABA-4AA8-4EC1-83B2-11781EF3EF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="229">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Establish architecture, requirements, acceptance criteria, use cases and SDLC approach</t>
   </si>
   <si>
-    <t>Implement remaining preprocessing capabilities</t>
-  </si>
-  <si>
     <t>Investigate and prototype large-dataset processing</t>
   </si>
   <si>
@@ -708,6 +705,30 @@
   </si>
   <si>
     <t>In progress</t>
+  </si>
+  <si>
+    <t>M5T7</t>
+  </si>
+  <si>
+    <t>Implement remaining preprocessing capabilities along with analysis</t>
+  </si>
+  <si>
+    <t>Analysis Modules</t>
+  </si>
+  <si>
+    <t>Large section, implement EDA contents</t>
+  </si>
+  <si>
+    <t>Dataset loading, Basic Preprocessing</t>
+  </si>
+  <si>
+    <t>new need, yet to be discussed</t>
+  </si>
+  <si>
+    <t>26/08/2026 (full)</t>
+  </si>
+  <si>
+    <t>26/08/2026 (major)</t>
   </si>
 </sst>
 </file>
@@ -759,12 +780,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -794,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -828,6 +855,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1122,16 +1158,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -1139,16 +1175,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>19</v>
@@ -1156,16 +1192,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>19</v>
@@ -1173,16 +1209,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>19</v>
@@ -1190,16 +1226,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -1207,16 +1243,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>19</v>
@@ -1224,16 +1260,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>19</v>
@@ -1241,19 +1277,19 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1333,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1342,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1356,16 +1392,16 @@
         <v>51</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>19</v>
@@ -1385,16 +1421,16 @@
         <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1408,22 +1444,22 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>19</v>
@@ -1443,22 +1479,22 @@
         <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1466,28 +1502,28 @@
         <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>53</v>
+        <v>222</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7">
         <v>46121</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1498,25 +1534,25 @@
         <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1524,28 +1560,28 @@
         <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1556,25 +1592,25 @@
         <v>31</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1662,31 +1698,31 @@
         <v>33</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1697,31 +1733,31 @@
         <v>35</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1732,31 +1768,31 @@
         <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1767,31 +1803,31 @@
         <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1802,31 +1838,31 @@
         <v>38</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1837,31 +1873,31 @@
         <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1872,31 +1908,31 @@
         <v>40</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1907,31 +1943,31 @@
         <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2017,212 +2053,212 @@
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2294,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2308,13 +2344,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>49</v>
@@ -2329,27 +2365,27 @@
         <v>46089</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>49</v>
@@ -2364,27 +2400,27 @@
         <v>46120</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>49</v>
@@ -2399,27 +2435,27 @@
         <v>46120</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
@@ -2434,27 +2470,27 @@
         <v>46120</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
@@ -2469,121 +2505,121 @@
         <v>46120</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2669,352 +2705,352 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3031,7 +3067,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
@@ -3045,12 +3081,13 @@
     <col min="9" max="9" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="12" max="12" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3063,7 +3100,7 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3098,155 +3135,155 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="I5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
@@ -3255,57 +3292,87 @@
         <v>46031</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="14">
+        <v>46121</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="B9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="7">
         <v>46121</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>97</v>
+      <c r="F9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/9-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/9-Project_Plan/9-Project_Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\9-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240A7ABA-4AA8-4EC1-83B2-11781EF3EF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BEFF71-8D7A-439B-AB4D-22F562FAD1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="233">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -671,9 +671,6 @@
     <t>Scale the numeric data with 2 methods</t>
   </si>
   <si>
-    <t>Normalize the numeric data with 2 methods</t>
-  </si>
-  <si>
     <t>Create heatmap and p values for PCC method and handle dropping columns</t>
   </si>
   <si>
@@ -716,9 +713,6 @@
     <t>Analysis Modules</t>
   </si>
   <si>
-    <t>Large section, implement EDA contents</t>
-  </si>
-  <si>
     <t>Dataset loading, Basic Preprocessing</t>
   </si>
   <si>
@@ -729,6 +723,24 @@
   </si>
   <si>
     <t>26/08/2026 (major)</t>
+  </si>
+  <si>
+    <t>Normalize the numeric data with zscore (standardscaler)</t>
+  </si>
+  <si>
+    <t>Major section, implement EDA contents</t>
+  </si>
+  <si>
+    <t>Project Plant excel sheet</t>
+  </si>
+  <si>
+    <t>Project Plan</t>
+  </si>
+  <si>
+    <t>Primitive document for EDA</t>
+  </si>
+  <si>
+    <t>Data Analysis Draft</t>
   </si>
 </sst>
 </file>
@@ -853,9 +865,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -864,6 +873,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1161,7 +1173,7 @@
         <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>60</v>
@@ -1289,22 +1301,42 @@
         <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -1378,7 +1410,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1494,7 +1526,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1505,7 +1537,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>92</v>
@@ -1523,7 +1555,7 @@
         <v>162</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1537,22 +1569,22 @@
         <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1566,22 +1598,22 @@
         <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1595,22 +1627,22 @@
         <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1641,19 +1673,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2002,19 +2034,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2293,19 +2325,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2654,19 +2686,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3086,19 +3118,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3149,7 +3181,7 @@
         <v>49</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>19</v>
@@ -3184,7 +3216,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>19</v>
@@ -3193,7 +3225,7 @@
         <v>92</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>96</v>
@@ -3219,16 +3251,16 @@
         <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>96</v>
@@ -3248,22 +3280,22 @@
         <v>203</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>96</v>
@@ -3283,7 +3315,7 @@
         <v>204</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
@@ -3292,63 +3324,65 @@
         <v>46031</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>96</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46121</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="I8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="14">
-        <v>46121</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>49</v>
@@ -3357,7 +3391,7 @@
         <v>46121</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>96</v>
